--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Temas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7971,9 +7971,13 @@
         </is>
       </c>
       <c r="D396" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E396" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:30:51 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -8792,9 +8792,13 @@
         </is>
       </c>
       <c r="D439" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E439" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:32:53 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -17764,9 +17764,13 @@
         </is>
       </c>
       <c r="D911" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E911" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E911" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:44:53 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="912">
       <c r="A912" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -16415,9 +16415,13 @@
         </is>
       </c>
       <c r="D840" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E840" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E840" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:50:27 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="841">
       <c r="A841" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -1131,9 +1131,13 @@
         </is>
       </c>
       <c r="D36" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:55:44 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -22754,9 +22754,13 @@
         </is>
       </c>
       <c r="D1173" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1173" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1173" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 17:08:33 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1174">
       <c r="A1174" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -15184,9 +15184,13 @@
         </is>
       </c>
       <c r="D775" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E775" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E775" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 18:45:27 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="776">
       <c r="A776" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -20421,9 +20421,13 @@
         </is>
       </c>
       <c r="D1050" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1050" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1050" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 18:54:02 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1051">
       <c r="A1051" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -19395,9 +19395,13 @@
         </is>
       </c>
       <c r="D996" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E996" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E996" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 19:00:31 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="997">
       <c r="A997" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -20885,9 +20885,13 @@
         </is>
       </c>
       <c r="D1074" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1074" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1074" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 22:51:29 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1075">
       <c r="A1075" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -9541,9 +9541,13 @@
         </is>
       </c>
       <c r="D478" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E478" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 11:49:57 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -12870,9 +12870,13 @@
         </is>
       </c>
       <c r="D653" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E653" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E653" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:32:45 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -3491,9 +3491,13 @@
         </is>
       </c>
       <c r="D160" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E160" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 16:11:08 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -25161,9 +25161,13 @@
         </is>
       </c>
       <c r="D1298" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1298" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1298" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 23:03:07 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1299">
       <c r="A1299" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -1971,9 +1971,13 @@
         </is>
       </c>
       <c r="D80" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E80" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 12:04:39 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -21741,9 +21741,13 @@
         </is>
       </c>
       <c r="D1118" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1118" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1118" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 16:21:44 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1119">
       <c r="A1119" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -14212,9 +14212,13 @@
         </is>
       </c>
       <c r="D723" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E723" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E723" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 16:25:03 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -5646,9 +5646,13 @@
         </is>
       </c>
       <c r="D273" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E273" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 23:07:23 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -6049,9 +6049,13 @@
         </is>
       </c>
       <c r="D294" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E294" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22 15:25:30 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -3039,9 +3039,13 @@
         </is>
       </c>
       <c r="D136" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E136" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:15:30 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -12738,9 +12738,13 @@
         </is>
       </c>
       <c r="D645" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E645" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E645" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22 22:49:20 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -4966,9 +4966,13 @@
         </is>
       </c>
       <c r="D237" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E237" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23 11:15:47 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -24756,9 +24756,13 @@
         </is>
       </c>
       <c r="D1275" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1275" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1275" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23 16:30:00 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1276">
       <c r="A1276" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -24931,9 +24931,13 @@
         </is>
       </c>
       <c r="D1284" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1284" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1284" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23 22:16:02 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1285">
       <c r="A1285" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -25566,9 +25566,13 @@
         </is>
       </c>
       <c r="D1317" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1317" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1317" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:48:14 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1318">
       <c r="A1318" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -12400,9 +12400,13 @@
         </is>
       </c>
       <c r="D627" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E627" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E627" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:25:36 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -21636,9 +21636,13 @@
         </is>
       </c>
       <c r="D1111" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1111" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1111" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:18 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1112">
       <c r="A1112" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -12575,9 +12575,13 @@
         </is>
       </c>
       <c r="D636" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E636" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E636" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:41:12 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -1154,9 +1154,13 @@
         </is>
       </c>
       <c r="D37" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25 16:29:59 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -9763,9 +9763,13 @@
         </is>
       </c>
       <c r="D488" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E488" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E488" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:23:05 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -19204,9 +19204,13 @@
         </is>
       </c>
       <c r="D983" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E983" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E983" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26 10:51:03 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="984">
       <c r="A984" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -20295,9 +20295,13 @@
         </is>
       </c>
       <c r="D1040" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1040" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1040" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26 16:22:06 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1041">
       <c r="A1041" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -21314,9 +21314,13 @@
         </is>
       </c>
       <c r="D1093" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1093" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1093" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:15:49 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1094">
       <c r="A1094" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -6483,9 +6483,13 @@
         </is>
       </c>
       <c r="D316" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E316" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27 10:07:21 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -5031,9 +5031,13 @@
         </is>
       </c>
       <c r="D240" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E240" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27 15:19:25 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -20980,9 +20980,13 @@
         </is>
       </c>
       <c r="D1075" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1075" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1075" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27 22:04:31 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1076">
       <c r="A1076" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -10060,9 +10060,13 @@
         </is>
       </c>
       <c r="D503" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E503" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E503" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28 10:27:34 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -25827,9 +25827,13 @@
         </is>
       </c>
       <c r="D1328" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1328" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1328" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28 15:21:57 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1329">
       <c r="A1329" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -14739,9 +14739,13 @@
         </is>
       </c>
       <c r="D748" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E748" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E748" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28 22:04:13 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="749">
       <c r="A749" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -8338,9 +8338,13 @@
         </is>
       </c>
       <c r="D413" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E413" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:31:12 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -24527,9 +24527,13 @@
         </is>
       </c>
       <c r="D1260" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1260" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1260" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29 16:55:45 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1261">
       <c r="A1261" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -23634,9 +23634,13 @@
         </is>
       </c>
       <c r="D1213" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1213" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1213" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29 22:10:07 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1214">
       <c r="A1214" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -11778,9 +11778,13 @@
         </is>
       </c>
       <c r="D593" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E593" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E593" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30 10:56:41 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -21190,9 +21190,13 @@
         </is>
       </c>
       <c r="D1085" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1085" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1085" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:25:42 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1086">
       <c r="A1086" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -15496,9 +15496,13 @@
         </is>
       </c>
       <c r="D787" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E787" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E787" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30 22:16:53 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="788">
       <c r="A788" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -2264,9 +2264,13 @@
         </is>
       </c>
       <c r="D95" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E95" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:23:23 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -7179,9 +7179,13 @@
         </is>
       </c>
       <c r="D352" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E352" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01 16:29:50 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -20160,9 +20160,13 @@
         </is>
       </c>
       <c r="D1031" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1031" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1031" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01 22:19:19 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1032">
       <c r="A1032" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -11102,9 +11102,13 @@
         </is>
       </c>
       <c r="D557" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E557" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E557" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02 10:37:40 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -25392,9 +25392,13 @@
         </is>
       </c>
       <c r="D1303" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1303" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1303" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:08:09 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1304">
       <c r="A1304" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -7620,9 +7620,13 @@
         </is>
       </c>
       <c r="D375" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E375" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 10:34:55 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -15261,9 +15261,13 @@
         </is>
       </c>
       <c r="D774" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E774" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E774" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 15:55:13 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="775">
       <c r="A775" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -11509,9 +11509,13 @@
         </is>
       </c>
       <c r="D578" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E578" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E578" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:06:35 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -12935,9 +12935,13 @@
         </is>
       </c>
       <c r="D652" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E652" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E652" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:09:05 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -18082,9 +18082,13 @@
         </is>
       </c>
       <c r="D921" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E921" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E921" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:00:31 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="922">
       <c r="A922" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -26849,9 +26849,13 @@
         </is>
       </c>
       <c r="D1378" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1378" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1378" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05 10:11:53 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1379">
       <c r="A1379" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -12011,9 +12011,13 @@
         </is>
       </c>
       <c r="D604" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E604" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E604" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05 22:03:39 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -827,9 +827,13 @@
         </is>
       </c>
       <c r="D20" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06 12:04:31 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -9046,9 +9046,13 @@
         </is>
       </c>
       <c r="D449" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E449" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06 22:15:10 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -2918,9 +2918,13 @@
         </is>
       </c>
       <c r="D129" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E129" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 10:54:48 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -4564,9 +4564,13 @@
         </is>
       </c>
       <c r="D215" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E215" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08 10:15:38 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -23436,9 +23436,13 @@
         </is>
       </c>
       <c r="D1199" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1199" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1199" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 10:53:44 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1200">
       <c r="A1200" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -24451,9 +24451,13 @@
         </is>
       </c>
       <c r="D1252" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1252" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1252" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:52:14 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1253">
       <c r="A1253" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -23516,9 +23516,13 @@
         </is>
       </c>
       <c r="D1203" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1203" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1203" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11 09:27:42 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1204">
       <c r="A1204" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -13514,9 +13514,13 @@
         </is>
       </c>
       <c r="D681" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E681" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E681" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12 09:50:02 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -18623,9 +18623,13 @@
         </is>
       </c>
       <c r="D948" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E948" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E948" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 10:59:35 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="949">
       <c r="A949" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -5986,9 +5986,13 @@
         </is>
       </c>
       <c r="D289" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E289" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:57:20 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -4644,9 +4644,13 @@
         </is>
       </c>
       <c r="D219" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E219" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 10:01:49 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -20011,9 +20011,13 @@
         </is>
       </c>
       <c r="D1020" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1020" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1020" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:07:49 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1021">
       <c r="A1021" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -4705,9 +4705,13 @@
         </is>
       </c>
       <c r="D222" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E222" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17 09:56:07 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -16153,9 +16153,13 @@
         </is>
       </c>
       <c r="D818" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E818" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E818" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18 09:23:41 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="819">
       <c r="A819" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -20274,9 +20274,13 @@
         </is>
       </c>
       <c r="D1033" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1033" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1033" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 09:51:06 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1034">
       <c r="A1034" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -24704,9 +24704,13 @@
         </is>
       </c>
       <c r="D1263" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1263" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1263" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 10:51:00 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1264">
       <c r="A1264" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -22571,9 +22571,13 @@
         </is>
       </c>
       <c r="D1152" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1152" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1152" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21 10:24:47 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1153">
       <c r="A1153" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -21008,9 +21008,13 @@
         </is>
       </c>
       <c r="D1071" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1071" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1071" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22 10:24:49 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1072">
       <c r="A1072" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -24020,9 +24020,13 @@
         </is>
       </c>
       <c r="D1227" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1227" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23 10:21:36 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1228">
       <c r="A1228" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -15716,9 +15716,13 @@
         </is>
       </c>
       <c r="D795" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E795" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E795" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24 10:15:21 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="796">
       <c r="A796" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -18012,9 +18012,13 @@
         </is>
       </c>
       <c r="D915" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E915" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E915" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26 09:57:46 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="916">
       <c r="A916" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -2614,9 +2614,13 @@
         </is>
       </c>
       <c r="D113" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E113" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27 11:18:55 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -19343,9 +19343,13 @@
         </is>
       </c>
       <c r="D984" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E984" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E984" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28 10:33:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="985">
       <c r="A985" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -19826,9 +19826,13 @@
         </is>
       </c>
       <c r="D1009" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1009" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1009" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 10:37:24 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1010">
       <c r="A1010" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -24405,9 +24405,13 @@
         </is>
       </c>
       <c r="D1246" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1246" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1246" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 10:23:59 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1247">
       <c r="A1247" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -7937,9 +7937,13 @@
         </is>
       </c>
       <c r="D390" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E390" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31 10:37:32 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -16895,9 +16895,13 @@
         </is>
       </c>
       <c r="D856" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E856" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E856" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01 09:58:02 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="857">
       <c r="A857" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -3960,9 +3960,13 @@
         </is>
       </c>
       <c r="D183" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E183" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02 09:55:13 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -10766,9 +10766,13 @@
         </is>
       </c>
       <c r="D537" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E537" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E537" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 10:37:03 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -26779,9 +26779,13 @@
         </is>
       </c>
       <c r="D1368" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1368" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1368" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05 10:33:11 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1369">
       <c r="A1369" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -10709,9 +10709,13 @@
         </is>
       </c>
       <c r="D534" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E534" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E534" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06 10:37:30 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -20953,9 +20953,13 @@
         </is>
       </c>
       <c r="D1066" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1066" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1066" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07 08:58:13 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1067">
       <c r="A1067" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -9002,9 +9002,13 @@
         </is>
       </c>
       <c r="D445" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E445" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:38:27 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -21037,9 +21037,13 @@
         </is>
       </c>
       <c r="D1070" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1070" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1070" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09 08:42:21 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1071">
       <c r="A1071" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -22878,9 +22878,13 @@
         </is>
       </c>
       <c r="D1165" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1165" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:18:14 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1166">
       <c r="A1166" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -13649,9 +13649,13 @@
         </is>
       </c>
       <c r="D686" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E686" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E686" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11 08:53:32 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -6660,9 +6660,13 @@
         </is>
       </c>
       <c r="D323" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E323" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12 09:10:11 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -13098,9 +13098,13 @@
         </is>
       </c>
       <c r="D657" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E657" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E657" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 11:51:55 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -24434,9 +24434,13 @@
         </is>
       </c>
       <c r="D1245" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1245" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1245" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14 09:06:10 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1246">
       <c r="A1246" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -2789,9 +2789,13 @@
         </is>
       </c>
       <c r="D122" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E122" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15 08:25:41 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -6128,9 +6128,13 @@
         </is>
       </c>
       <c r="D295" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E295" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16 08:26:53 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -22457,9 +22457,13 @@
         </is>
       </c>
       <c r="D1142" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1142" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:41:12 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1143">
       <c r="A1143" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -25949,9 +25949,13 @@
         </is>
       </c>
       <c r="D1322" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1322" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1322" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 08:34:41 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1323">
       <c r="A1323" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -10174,9 +10174,13 @@
         </is>
       </c>
       <c r="D505" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E505" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E505" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:35:24 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -6360,9 +6360,13 @@
         </is>
       </c>
       <c r="D307" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E307" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:36:03 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -11239,9 +11239,13 @@
         </is>
       </c>
       <c r="D560" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E560" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E560" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21 08:37:59 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -24325,9 +24325,13 @@
         </is>
       </c>
       <c r="D1238" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1238" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1238" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22 08:26:32 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1239">
       <c r="A1239" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -20118,9 +20118,13 @@
         </is>
       </c>
       <c r="D1021" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1021" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1021" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23 08:26:38 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1022">
       <c r="A1022" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -561,9 +561,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24 08:45:55 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -20883,9 +20883,13 @@
         </is>
       </c>
       <c r="D1060" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1060" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1060" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25 08:39:34 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1061">
       <c r="A1061" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -7212,9 +7212,13 @@
         </is>
       </c>
       <c r="D351" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E351" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 08:40:37 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -5094,9 +5094,13 @@
         </is>
       </c>
       <c r="D241" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E241" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 19:53:53 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -1869,9 +1869,13 @@
         </is>
       </c>
       <c r="D74" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E74" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29 13:37:36 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -24981,9 +24981,13 @@
         </is>
       </c>
       <c r="D1270" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1270" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1270" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30 13:32:31 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1271">
       <c r="A1271" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -10350,9 +10350,13 @@
         </is>
       </c>
       <c r="D513" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E513" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E513" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:50:48 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -16868,9 +16868,13 @@
         </is>
       </c>
       <c r="D851" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E851" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E851" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:05:31 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="852">
       <c r="A852" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -11179,9 +11179,13 @@
         </is>
       </c>
       <c r="D556" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E556" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E556" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:33:01 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="n">
